--- a/ig/ekg/StructureDefinition-medcom-ekg-recording-observation.xlsx
+++ b/ig/ekg/StructureDefinition-medcom-ekg-recording-observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.2</t>
+    <t>2.0.0-trial-use-2026-04-28</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T10:08:45+00:00</t>
+    <t>2026-04-29T09:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -701,7 +701,7 @@
 </t>
   </si>
   <si>
-    <t>Base64-encoded content of the EKG recording PDF/A document.</t>
+    <t>Base64-encoded content of the EKG recording PDF document.</t>
   </si>
   <si>
     <t>The actual data of the attachment - a sequence of bytes, base64 encoded.</t>
@@ -2156,7 +2156,7 @@
 </t>
   </si>
   <si>
-    <t>Free-text note, used to document relevant measurement-related remarks. Line breaks in FHIR string values must be represented as escaped newline characters \n in JSON and either as a literal newline in the element text or as the character reference &amp;#xA; in XML.</t>
+    <t>Free-text note, used to document relevant measurement-related remarks. Line breaks must be represented as escaped newline characters \n in JSON and as the character reference &amp;#xA; in XML.</t>
   </si>
   <si>
     <t>Comments about the observation or the results.</t>

--- a/ig/ekg/StructureDefinition-medcom-ekg-recording-observation.xlsx
+++ b/ig/ekg/StructureDefinition-medcom-ekg-recording-observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-trial-use-2026-04-28</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:39:42+00:00</t>
+    <t>2026-06-04T11:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
